--- a/Experiment Key.xlsx
+++ b/Experiment Key.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schle\Documents\GitHub\CoffeyBehavior_RatEdition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coffeeadmin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D2119F-4A83-4583-8FB2-478004858E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D37C61C-14A6-4F65-876C-E265BFFA9E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD7F1C8E-C617-4CB6-9DA2-6C0677DD65A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CD7F1C8E-C617-4CB6-9DA2-6C0677DD65A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="36">
   <si>
     <t>Run</t>
   </si>
@@ -53,38 +53,104 @@
     <t>Session Type</t>
   </si>
   <si>
+    <t>Fentanyl Concentration (ug/ml)</t>
+  </si>
+  <si>
+    <t>Volume per dose (mL)</t>
+  </si>
+  <si>
     <t>ER</t>
   </si>
   <si>
+    <t>PreTraining</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
     <t>Extinction</t>
   </si>
   <si>
-    <t>PreTraining</t>
-  </si>
-  <si>
-    <t>Training</t>
+    <t>4/23/2025</t>
   </si>
   <si>
     <t>Reinstatement</t>
   </si>
   <si>
-    <t>Fentanyl Concentration (ug/ml)</t>
-  </si>
-  <si>
-    <t>Volume per dose (mL)</t>
-  </si>
-  <si>
-    <t>`</t>
-  </si>
-  <si>
-    <t>4/23/2025</t>
+    <t>Pretraining</t>
+  </si>
+  <si>
+    <t>6/9/2026</t>
+  </si>
+  <si>
+    <t>6/10/2026</t>
+  </si>
+  <si>
+    <t>6/11/2026</t>
+  </si>
+  <si>
+    <t>6/12/2026</t>
+  </si>
+  <si>
+    <t>6/13/2026</t>
+  </si>
+  <si>
+    <t>6/16/2026</t>
+  </si>
+  <si>
+    <t>6/17/2026</t>
+  </si>
+  <si>
+    <t>6/18/2026</t>
+  </si>
+  <si>
+    <t>6/19/2026</t>
+  </si>
+  <si>
+    <t>6/20/2026</t>
+  </si>
+  <si>
+    <t>6/23/2026</t>
+  </si>
+  <si>
+    <t>6/24/2026</t>
+  </si>
+  <si>
+    <t>6/25/2026</t>
+  </si>
+  <si>
+    <t>6/26/2026</t>
+  </si>
+  <si>
+    <t>6/27/2026</t>
+  </si>
+  <si>
+    <t>6/30/2026</t>
+  </si>
+  <si>
+    <t>7/1/2026</t>
+  </si>
+  <si>
+    <t>7/2/2026</t>
+  </si>
+  <si>
+    <t>7/3/2026</t>
+  </si>
+  <si>
+    <t>7/4/2026</t>
+  </si>
+  <si>
+    <t>7/7/2026</t>
+  </si>
+  <si>
+    <t>7/8/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,7 +181,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -218,11 +284,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -257,12 +345,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -278,17 +360,20 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,6 +508,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -451,13 +543,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -492,8 +577,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66D5D3F3-56B7-46A6-A496-8A38EB2958B8}" name="Table1" displayName="Table1" ref="A1:G142" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G142" xr:uid="{66D5D3F3-56B7-46A6-A496-8A38EB2958B8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66D5D3F3-56B7-46A6-A496-8A38EB2958B8}" name="Table1" displayName="Table1" ref="A1:G86" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8">
+  <autoFilter ref="A1:G86" xr:uid="{66D5D3F3-56B7-46A6-A496-8A38EB2958B8}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{AC6BF73A-E8FB-4DE1-8466-D18151A4B8E7}" name="Run" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{C1A30F8F-799D-4454-AF86-7FDC3D02C95A}" name="Experiment" dataDxfId="5"/>
@@ -824,8 +909,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB0A6A4-2587-470F-932D-101544863E20}">
-  <dimension ref="A1:G142"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G86"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
@@ -840,7 +925,7 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="29.45" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -857,1142 +942,1719 @@
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="18">
+        <v>7</v>
+      </c>
+      <c r="C2" s="16">
         <v>45737</v>
       </c>
       <c r="D2" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G2" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="10">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="18">
+        <v>7</v>
+      </c>
+      <c r="C3" s="16">
         <v>45740</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1">
         <v>70</v>
       </c>
-      <c r="G3" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G3" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="10">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="18">
+        <v>7</v>
+      </c>
+      <c r="C4" s="16">
         <v>45741</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1">
         <v>70</v>
       </c>
-      <c r="G4" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G4" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="18">
+        <v>7</v>
+      </c>
+      <c r="C5" s="16">
         <v>45742</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1">
         <v>70</v>
       </c>
-      <c r="G5" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="10">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="18">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16">
         <v>45743</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1">
         <v>70</v>
       </c>
-      <c r="G6" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="10">
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="18">
+        <v>7</v>
+      </c>
+      <c r="C7" s="16">
         <v>45744</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1">
         <v>70</v>
       </c>
-      <c r="G7" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="18">
+        <v>7</v>
+      </c>
+      <c r="C8" s="16">
         <v>45747</v>
       </c>
       <c r="D8" s="1">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1">
         <v>70</v>
       </c>
-      <c r="G8" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G8" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="10">
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="18">
+        <v>7</v>
+      </c>
+      <c r="C9" s="16">
         <v>45748</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1">
         <v>70</v>
       </c>
-      <c r="G9" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="10">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="18">
+        <v>7</v>
+      </c>
+      <c r="C10" s="16">
         <v>45749</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1">
         <v>70</v>
       </c>
-      <c r="G10" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="10">
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="18">
+        <v>7</v>
+      </c>
+      <c r="C11" s="16">
         <v>45750</v>
       </c>
       <c r="D11" s="1">
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1">
         <v>70</v>
       </c>
-      <c r="G11" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G11" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="10">
         <v>1</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="18">
+        <v>7</v>
+      </c>
+      <c r="C12" s="16">
         <v>45751</v>
       </c>
       <c r="D12" s="1">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1">
         <v>70</v>
       </c>
-      <c r="G12" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="10">
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="18">
+        <v>7</v>
+      </c>
+      <c r="C13" s="16">
         <v>45754</v>
       </c>
       <c r="D13" s="1">
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1">
         <v>70</v>
       </c>
-      <c r="G13" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="10">
         <v>1</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="18">
+        <v>7</v>
+      </c>
+      <c r="C14" s="16">
         <v>45755</v>
       </c>
       <c r="D14" s="1">
         <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1">
         <v>70</v>
       </c>
-      <c r="G14" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="10">
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="18">
+        <v>7</v>
+      </c>
+      <c r="C15" s="16">
         <v>45756</v>
       </c>
       <c r="D15" s="1">
         <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1">
         <v>70</v>
       </c>
-      <c r="G15" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="10">
         <v>1</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="18">
+        <v>7</v>
+      </c>
+      <c r="C16" s="16">
         <v>45757</v>
       </c>
       <c r="D16" s="1">
         <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1">
         <v>70</v>
       </c>
-      <c r="G16" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="10">
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="18">
+        <v>7</v>
+      </c>
+      <c r="C17" s="16">
         <v>45758</v>
       </c>
       <c r="D17" s="1">
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1">
         <v>70</v>
       </c>
-      <c r="G17" s="15">
-        <v>1.9310000000000001E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="13">
+        <v>4.8259999999999997E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="10">
         <v>1</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="18">
+        <v>7</v>
+      </c>
+      <c r="C18" s="16">
         <v>45761</v>
       </c>
       <c r="D18" s="1">
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
-      <c r="G18" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="10">
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="18">
+        <v>7</v>
+      </c>
+      <c r="C19" s="16">
         <v>45762</v>
       </c>
       <c r="D19" s="1">
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
-      <c r="G19" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="18">
+        <v>7</v>
+      </c>
+      <c r="C20" s="16">
         <v>45763</v>
       </c>
       <c r="D20" s="1">
         <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
-      <c r="G20" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="10">
         <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="18">
+        <v>7</v>
+      </c>
+      <c r="C21" s="16">
         <v>45764</v>
       </c>
       <c r="D21" s="1">
         <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
-      <c r="G21" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="10">
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="18">
+        <v>7</v>
+      </c>
+      <c r="C22" s="16">
         <v>45765</v>
       </c>
       <c r="D22" s="1">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
-      <c r="G22" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="10">
         <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="18">
+        <v>7</v>
+      </c>
+      <c r="C23" s="16">
         <v>45768</v>
       </c>
       <c r="D23" s="1">
         <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
-      <c r="G23" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G23" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="10">
         <v>1</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="18">
+        <v>7</v>
+      </c>
+      <c r="C24" s="16">
         <v>45769</v>
       </c>
       <c r="D24" s="1">
         <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="10">
+        <v>1</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1">
+        <v>23</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1">
+      <c r="A26" s="10">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="16">
+        <v>45771</v>
+      </c>
+      <c r="D26" s="1">
+        <v>24</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="17">
+        <v>2</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="18">
+        <v>45898</v>
+      </c>
+      <c r="D27" s="11">
+        <v>-1</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="11">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="10">
+        <v>2</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="16">
+        <v>45901</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="1">
+        <v>70</v>
+      </c>
+      <c r="G28" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="10">
+        <v>2</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="16">
+        <v>45902</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1">
+        <v>70</v>
+      </c>
+      <c r="G29" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="10">
+        <v>2</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="16">
+        <v>45903</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1">
+        <v>70</v>
+      </c>
+      <c r="G30" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="10">
+        <v>2</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="16">
+        <v>45904</v>
+      </c>
+      <c r="D31" s="1">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1">
+        <v>70</v>
+      </c>
+      <c r="G31" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="10">
+        <v>2</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="16">
+        <v>45905</v>
+      </c>
+      <c r="D32" s="1">
+        <v>5</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1">
+        <v>70</v>
+      </c>
+      <c r="G32" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="10">
+        <v>2</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="16">
+        <v>45909</v>
+      </c>
+      <c r="D33" s="1">
         <v>6</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="E33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="1">
+        <v>70</v>
+      </c>
+      <c r="G33" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="10">
+        <v>2</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="16">
+        <v>45910</v>
+      </c>
+      <c r="D34" s="1">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="1">
+        <v>70</v>
+      </c>
+      <c r="G34" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="10">
+        <v>2</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="16">
+        <v>45911</v>
+      </c>
+      <c r="D35" s="1">
+        <v>8</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="1">
+        <v>70</v>
+      </c>
+      <c r="G35" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="10">
+        <v>2</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="16">
+        <v>45912</v>
+      </c>
+      <c r="D36" s="1">
+        <v>9</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="1">
+        <v>70</v>
+      </c>
+      <c r="G36" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="10">
+        <v>2</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="16">
+        <v>45913</v>
+      </c>
+      <c r="D37" s="1">
+        <v>10</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="1">
+        <v>70</v>
+      </c>
+      <c r="G37" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="10">
+        <v>2</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="16">
+        <v>45915</v>
+      </c>
+      <c r="D38" s="1">
+        <v>11</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="1">
+        <v>70</v>
+      </c>
+      <c r="G38" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="10">
+        <v>2</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="16">
+        <v>45916</v>
+      </c>
+      <c r="D39" s="1">
         <v>12</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="E39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="1">
+        <v>70</v>
+      </c>
+      <c r="G39" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>2</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="16">
+        <v>45917</v>
+      </c>
+      <c r="D40" s="1">
+        <v>13</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="1">
+        <v>70</v>
+      </c>
+      <c r="G40" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>2</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="16">
+        <v>45918</v>
+      </c>
+      <c r="D41" s="1">
+        <v>14</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1">
+        <v>70</v>
+      </c>
+      <c r="G41" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>2</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="16">
+        <v>45919</v>
+      </c>
+      <c r="D42" s="1">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="1">
+        <v>70</v>
+      </c>
+      <c r="G42" s="13">
+        <v>4.8939999999999997E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>2</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="16">
+        <v>45922</v>
+      </c>
+      <c r="D43" s="1">
+        <v>16</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>2</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="16">
+        <v>45923</v>
+      </c>
+      <c r="D44" s="1">
+        <v>17</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>2</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="16">
+        <v>45924</v>
+      </c>
+      <c r="D45" s="1">
+        <v>18</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="10">
+        <v>2</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="16">
+        <v>45925</v>
+      </c>
+      <c r="D46" s="1">
+        <v>19</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="10">
+        <v>2</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="16">
+        <v>45926</v>
+      </c>
+      <c r="D47" s="1">
+        <v>20</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="10">
+        <v>2</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="16">
+        <v>45929</v>
+      </c>
+      <c r="D48" s="1">
+        <v>21</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="10">
+        <v>2</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="16">
+        <v>45930</v>
+      </c>
+      <c r="D49" s="1">
+        <v>22</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="10">
+        <v>2</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="16">
+        <v>45931</v>
+      </c>
+      <c r="D50" s="1">
+        <v>23</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1">
+      <c r="A51" s="14">
+        <v>2</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="20">
+        <v>45932</v>
+      </c>
+      <c r="D51" s="4">
+        <v>24</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="4">
+        <v>0</v>
+      </c>
+      <c r="G51" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="1">
+        <v>7</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="1">
+        <v>70</v>
+      </c>
+      <c r="G52" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15">
+      <c r="A53" s="1">
+        <v>7</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="1">
+        <v>70</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15">
+      <c r="A54" s="1">
+        <v>7</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="1">
+        <v>70</v>
+      </c>
+      <c r="G54" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15">
+      <c r="A55" s="1">
+        <v>7</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="1">
+        <v>4</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" s="1">
+        <v>70</v>
+      </c>
+      <c r="G55" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15">
+      <c r="A56" s="1">
+        <v>7</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="1">
         <v>5</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="E56" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="1">
+        <v>70</v>
+      </c>
+      <c r="G56" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15">
+      <c r="A57" s="1">
+        <v>7</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="1">
+        <v>6</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="1">
+        <v>70</v>
+      </c>
+      <c r="G57" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15">
+      <c r="A58" s="1">
+        <v>7</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="1">
+        <v>7</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="1">
+        <v>70</v>
+      </c>
+      <c r="G58" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15">
+      <c r="A59" s="1">
+        <v>7</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="1">
+        <v>8</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="1">
+        <v>70</v>
+      </c>
+      <c r="G59" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15">
+      <c r="A60" s="1">
+        <v>7</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" s="1">
+        <v>9</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="1">
+        <v>70</v>
+      </c>
+      <c r="G60" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15">
+      <c r="A61" s="1">
+        <v>7</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="1">
+        <v>10</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="1">
+        <v>70</v>
+      </c>
+      <c r="G61" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15">
+      <c r="A62" s="1">
+        <v>7</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="1">
+        <v>11</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="1">
+        <v>70</v>
+      </c>
+      <c r="G62" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15">
+      <c r="A63" s="1">
+        <v>7</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" s="1">
+        <v>12</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="1">
+        <v>70</v>
+      </c>
+      <c r="G63" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15">
+      <c r="A64" s="1">
+        <v>7</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="1">
         <v>13</v>
       </c>
-      <c r="D25" s="20">
-        <v>23</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="20">
-        <v>0</v>
-      </c>
-      <c r="G25" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="16">
-        <v>1</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="18">
-        <v>45771</v>
-      </c>
-      <c r="D26" s="4">
-        <v>24</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="4">
-        <v>0</v>
-      </c>
-      <c r="G26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="G27" s="15"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="G28" s="15"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="G29" s="15"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="G30" s="15"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="G31" s="15"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="G32" s="15"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="G33" s="15"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="G34" s="15"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="G35" s="15"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="G36" s="15"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="G37" s="15"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="G38" s="15"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="G39" s="15"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="G40" s="15"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="G41" s="15"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="G42" s="15"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="C43" s="2"/>
-      <c r="G43" s="15"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="C44" s="2"/>
-      <c r="G44" s="15"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
-      <c r="C45" s="2"/>
-      <c r="G45" s="15"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
-      <c r="C46" s="2"/>
-      <c r="G46" s="15"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
-      <c r="C47" s="2"/>
-      <c r="G47" s="15"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
-      <c r="C48" s="2"/>
-      <c r="G48" s="15"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
-      <c r="C49" s="2"/>
-      <c r="G49" s="15"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
-      <c r="C50" s="2"/>
-      <c r="G50" s="15"/>
-    </row>
-    <row r="51" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="10"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="15"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="15"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
-      <c r="C53" s="2"/>
-      <c r="G53" s="15"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="10"/>
-      <c r="C54" s="2"/>
-      <c r="G54" s="15"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="10"/>
-      <c r="C55" s="2"/>
-      <c r="G55" s="15"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="10"/>
-      <c r="C56" s="2"/>
-      <c r="G56" s="15"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="10"/>
-      <c r="C57" s="2"/>
-      <c r="G57" s="15"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="10"/>
-      <c r="C58" s="2"/>
-      <c r="G58" s="15"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="10"/>
-      <c r="C59" s="2"/>
-      <c r="G59" s="15"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="10"/>
-      <c r="C60" s="2"/>
-      <c r="G60" s="15"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
-      <c r="C61" s="2"/>
-      <c r="G61" s="15"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="10"/>
-      <c r="C62" s="2"/>
-      <c r="G62" s="15"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="10"/>
-      <c r="C63" s="2"/>
-      <c r="G63" s="15"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="10"/>
-      <c r="C64" s="2"/>
-      <c r="G64" s="15"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="10"/>
-      <c r="C65" s="2"/>
-      <c r="G65" s="15"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="10"/>
-      <c r="C66" s="2"/>
-      <c r="G66" s="15"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="10"/>
-      <c r="C67" s="2"/>
-      <c r="G67" s="15"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="10"/>
-      <c r="C68" s="2"/>
-      <c r="G68" s="15"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="10"/>
-      <c r="C69" s="2"/>
-      <c r="G69" s="15"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="10"/>
-      <c r="C70" s="2"/>
-      <c r="G70" s="15"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="10"/>
-      <c r="C71" s="2"/>
-      <c r="G71" s="15"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="10"/>
-      <c r="C72" s="2"/>
-      <c r="G72" s="15"/>
-    </row>
-    <row r="73" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="10"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="15"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="10"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="15"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="10"/>
+      <c r="E64" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="1">
+        <v>70</v>
+      </c>
+      <c r="G64" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15">
+      <c r="A65" s="1">
+        <v>7</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" s="1">
+        <v>14</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="1">
+        <v>70</v>
+      </c>
+      <c r="G65" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15">
+      <c r="A66" s="1">
+        <v>7</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="1">
+        <v>15</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="1">
+        <v>70</v>
+      </c>
+      <c r="G66" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="1">
+        <v>7</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="1">
+        <v>16</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5.1609700000000001E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15">
+      <c r="A68" s="1">
+        <v>7</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" s="1">
+        <v>17</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15">
+      <c r="A69" s="1">
+        <v>7</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="1">
+        <v>18</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15">
+      <c r="A70" s="1">
+        <v>7</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D70" s="1">
+        <v>19</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15">
+      <c r="A71" s="1">
+        <v>7</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" s="1">
+        <v>20</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15">
+      <c r="A72" s="1">
+        <v>7</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="1">
+        <v>21</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="1">
+        <v>7</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" s="1">
+        <v>22</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="C74" s="2"/>
+      <c r="E74" s="5"/>
+    </row>
+    <row r="75" spans="1:7">
       <c r="C75" s="2"/>
-      <c r="G75" s="15"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="10"/>
+      <c r="E75" s="5"/>
+    </row>
+    <row r="76" spans="1:7">
       <c r="C76" s="2"/>
-      <c r="G76" s="15"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="10"/>
+      <c r="E76" s="5"/>
+    </row>
+    <row r="77" spans="1:7">
       <c r="C77" s="2"/>
-      <c r="G77" s="15"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="10"/>
+      <c r="E77" s="5"/>
+    </row>
+    <row r="78" spans="1:7">
       <c r="C78" s="2"/>
-      <c r="G78" s="15"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="10"/>
+      <c r="E78" s="5"/>
+    </row>
+    <row r="79" spans="1:7">
       <c r="C79" s="2"/>
-      <c r="G79" s="15"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="10"/>
+      <c r="E79" s="5"/>
+    </row>
+    <row r="80" spans="1:7">
       <c r="C80" s="2"/>
-      <c r="G80" s="15"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="10"/>
+      <c r="E80" s="5"/>
+    </row>
+    <row r="81" spans="3:6">
       <c r="C81" s="2"/>
-      <c r="G81" s="15"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="10"/>
+      <c r="E81" s="5"/>
+    </row>
+    <row r="82" spans="3:6">
       <c r="C82" s="2"/>
-      <c r="G82" s="15"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="10"/>
+      <c r="E82" s="5"/>
+    </row>
+    <row r="83" spans="3:6">
       <c r="C83" s="2"/>
-      <c r="G83" s="15"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="10"/>
+      <c r="E83" s="5"/>
+    </row>
+    <row r="84" spans="3:6">
       <c r="C84" s="2"/>
-      <c r="G84" s="15"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="10"/>
+      <c r="E84" s="5"/>
+    </row>
+    <row r="85" spans="3:6">
       <c r="C85" s="2"/>
-      <c r="G85" s="15"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="10"/>
+      <c r="E85" s="5"/>
+    </row>
+    <row r="86" spans="3:6" ht="15" thickBot="1">
       <c r="C86" s="2"/>
-      <c r="G86" s="15"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="10"/>
-      <c r="C87" s="2"/>
-      <c r="G87" s="15"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="10"/>
-      <c r="C88" s="2"/>
-      <c r="G88" s="15"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="10"/>
-      <c r="C89" s="2"/>
-      <c r="G89" s="15"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="10"/>
-      <c r="C90" s="2"/>
-      <c r="G90" s="15"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="10"/>
-      <c r="C91" s="2"/>
-      <c r="G91" s="15"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="10"/>
-      <c r="C92" s="2"/>
-      <c r="G92" s="15"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="10"/>
-      <c r="C93" s="2"/>
-      <c r="G93" s="15"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="10"/>
-      <c r="C94" s="2"/>
-      <c r="G94" s="15"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="10"/>
-      <c r="C95" s="2"/>
-      <c r="G95" s="15"/>
-    </row>
-    <row r="96" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="10"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="12"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="15"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="10"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="13"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="15"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="10"/>
-      <c r="C98" s="2"/>
-      <c r="G98" s="15"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="10"/>
-      <c r="C99" s="2"/>
-      <c r="G99" s="15"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="10"/>
-      <c r="C100" s="2"/>
-      <c r="G100" s="15"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="10"/>
-      <c r="C101" s="2"/>
-      <c r="G101" s="15"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="10"/>
-      <c r="C102" s="2"/>
-      <c r="G102" s="15"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="10"/>
-      <c r="C103" s="2"/>
-      <c r="G103" s="15"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="10"/>
-      <c r="C104" s="2"/>
-      <c r="G104" s="15"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="10"/>
-      <c r="C105" s="2"/>
-      <c r="G105" s="15"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="10"/>
-      <c r="C106" s="2"/>
-      <c r="G106" s="15"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="10"/>
-      <c r="C107" s="2"/>
-      <c r="G107" s="15"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="10"/>
-      <c r="C108" s="2"/>
-      <c r="G108" s="15"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="10"/>
-      <c r="C109" s="2"/>
-      <c r="G109" s="15"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="10"/>
-      <c r="C110" s="2"/>
-      <c r="G110" s="15"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="10"/>
-      <c r="C111" s="2"/>
-      <c r="G111" s="15"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="10"/>
-      <c r="C112" s="2"/>
-      <c r="G112" s="15"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="10"/>
-      <c r="C113" s="2"/>
-      <c r="G113" s="15"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="10"/>
-      <c r="C114" s="2"/>
-      <c r="G114" s="15"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="10"/>
-      <c r="C115" s="2"/>
-      <c r="G115" s="15"/>
-    </row>
-    <row r="116" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="10"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="12"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="15"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C117" s="2"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C118" s="2"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C119" s="2"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C120" s="2"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C121" s="2"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C122" s="2"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C123" s="2"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C124" s="2"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C125" s="2"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C126" s="2"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C127" s="2"/>
-      <c r="E127" s="5"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C128" s="2"/>
-      <c r="E128" s="5"/>
-    </row>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C129" s="2"/>
-      <c r="E129" s="5"/>
-    </row>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C130" s="2"/>
-      <c r="E130" s="5"/>
-    </row>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C131" s="2"/>
-      <c r="E131" s="5"/>
-    </row>
-    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C132" s="2"/>
-      <c r="E132" s="5"/>
-    </row>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C133" s="2"/>
-      <c r="E133" s="5"/>
-    </row>
-    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C134" s="2"/>
-      <c r="E134" s="5"/>
-    </row>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C135" s="2"/>
-      <c r="E135" s="5"/>
-    </row>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C136" s="2"/>
-      <c r="E136" s="5"/>
-    </row>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C137" s="2"/>
-      <c r="E137" s="5"/>
-    </row>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C138" s="2"/>
-      <c r="E138" s="5"/>
-    </row>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C139" s="2"/>
-      <c r="E139" s="5"/>
-    </row>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C140" s="2"/>
-      <c r="E140" s="5"/>
-    </row>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C141" s="2"/>
-      <c r="E141" s="5"/>
-    </row>
-    <row r="142" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C142" s="2"/>
-      <c r="F142" s="4"/>
+      <c r="F86" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Experiment Key.xlsx
+++ b/Experiment Key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coffeeadmin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/16f162b2b74da370/Documents/GitHub/CoffeyBehavior_Rat_LHbTargets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D37C61C-14A6-4F65-876C-E265BFFA9E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{3D37C61C-14A6-4F65-876C-E265BFFA9E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{682F5EBB-2A69-43EB-B340-B85FAAA9A07A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CD7F1C8E-C617-4CB6-9DA2-6C0677DD65A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD7F1C8E-C617-4CB6-9DA2-6C0677DD65A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="38">
   <si>
     <t>Run</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Reinstatement</t>
   </si>
   <si>
-    <t>Pretraining</t>
-  </si>
-  <si>
     <t>6/9/2026</t>
   </si>
   <si>
@@ -144,13 +141,22 @@
   </si>
   <si>
     <t>7/8/2026</t>
+  </si>
+  <si>
+    <t>Weight Taken</t>
+  </si>
+  <si>
+    <t>7/9/2026</t>
+  </si>
+  <si>
+    <t>7/10/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,7 +187,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -254,30 +260,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -296,7 +282,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -306,11 +294,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -351,35 +374,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -508,13 +564,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -543,6 +592,13 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -577,16 +633,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66D5D3F3-56B7-46A6-A496-8A38EB2958B8}" name="Table1" displayName="Table1" ref="A1:G86" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8">
-  <autoFilter ref="A1:G86" xr:uid="{66D5D3F3-56B7-46A6-A496-8A38EB2958B8}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AC6BF73A-E8FB-4DE1-8466-D18151A4B8E7}" name="Run" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{C1A30F8F-799D-4454-AF86-7FDC3D02C95A}" name="Experiment" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{10669608-2E81-43C3-ACB0-E8F3716E758C}" name="Date" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{8231ECF3-FA36-4D2B-B9D2-B876D950D3FF}" name="Session" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{064861AC-CD6B-4377-A1E4-9F4A58A8B507}" name="Session Type" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{F33AC377-525A-4FF9-ADD6-F8A4D9B5F439}" name="Fentanyl Concentration (ug/ml)" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{F90B955B-0B18-4811-A232-903938BCEB82}" name="Volume per dose (mL)" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66D5D3F3-56B7-46A6-A496-8A38EB2958B8}" name="Table1" displayName="Table1" ref="A1:H86" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+  <autoFilter ref="A1:H86" xr:uid="{66D5D3F3-56B7-46A6-A496-8A38EB2958B8}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{AC6BF73A-E8FB-4DE1-8466-D18151A4B8E7}" name="Run" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C1A30F8F-799D-4454-AF86-7FDC3D02C95A}" name="Experiment" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{10669608-2E81-43C3-ACB0-E8F3716E758C}" name="Date" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{8231ECF3-FA36-4D2B-B9D2-B876D950D3FF}" name="Session" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{064861AC-CD6B-4377-A1E4-9F4A58A8B507}" name="Session Type" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{F33AC377-525A-4FF9-ADD6-F8A4D9B5F439}" name="Fentanyl Concentration (ug/ml)" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{F90B955B-0B18-4811-A232-903938BCEB82}" name="Volume per dose (mL)" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{C6B71B01-E45A-4C36-9804-196160711A2A}" name="Weight Taken" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -909,8 +966,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB0A6A4-2587-470F-932D-101544863E20}">
-  <dimension ref="A1:G86"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
@@ -925,7 +982,7 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29.45" thickBot="1">
+    <row r="1" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -947,19 +1004,22 @@
       <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="14">
         <v>45737</v>
       </c>
       <c r="D2" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -967,18 +1027,21 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="14">
         <v>45740</v>
       </c>
       <c r="D3" s="1">
@@ -990,18 +1053,21 @@
       <c r="F3" s="1">
         <v>70</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="14">
         <v>45741</v>
       </c>
       <c r="D4" s="1">
@@ -1013,18 +1079,21 @@
       <c r="F4" s="1">
         <v>70</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="14">
         <v>45742</v>
       </c>
       <c r="D5" s="1">
@@ -1036,18 +1105,21 @@
       <c r="F5" s="1">
         <v>70</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="14">
         <v>45743</v>
       </c>
       <c r="D6" s="1">
@@ -1059,18 +1131,21 @@
       <c r="F6" s="1">
         <v>70</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="14">
         <v>45744</v>
       </c>
       <c r="D7" s="1">
@@ -1082,18 +1157,21 @@
       <c r="F7" s="1">
         <v>70</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="14">
         <v>45747</v>
       </c>
       <c r="D8" s="1">
@@ -1105,18 +1183,21 @@
       <c r="F8" s="1">
         <v>70</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="14">
         <v>45748</v>
       </c>
       <c r="D9" s="1">
@@ -1128,18 +1209,21 @@
       <c r="F9" s="1">
         <v>70</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="14">
         <v>45749</v>
       </c>
       <c r="D10" s="1">
@@ -1151,18 +1235,21 @@
       <c r="F10" s="1">
         <v>70</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="14">
         <v>45750</v>
       </c>
       <c r="D11" s="1">
@@ -1174,18 +1261,21 @@
       <c r="F11" s="1">
         <v>70</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>1</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="14">
         <v>45751</v>
       </c>
       <c r="D12" s="1">
@@ -1197,18 +1287,21 @@
       <c r="F12" s="1">
         <v>70</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="14">
         <v>45754</v>
       </c>
       <c r="D13" s="1">
@@ -1220,18 +1313,21 @@
       <c r="F13" s="1">
         <v>70</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>1</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="14">
         <v>45755</v>
       </c>
       <c r="D14" s="1">
@@ -1243,18 +1339,21 @@
       <c r="F14" s="1">
         <v>70</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="14">
         <v>45756</v>
       </c>
       <c r="D15" s="1">
@@ -1266,18 +1365,21 @@
       <c r="F15" s="1">
         <v>70</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>1</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="14">
         <v>45757</v>
       </c>
       <c r="D16" s="1">
@@ -1289,18 +1391,21 @@
       <c r="F16" s="1">
         <v>70</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="14">
         <v>45758</v>
       </c>
       <c r="D17" s="1">
@@ -1312,18 +1417,21 @@
       <c r="F17" s="1">
         <v>70</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="1">
         <v>4.8259999999999997E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>1</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="14">
         <v>45761</v>
       </c>
       <c r="D18" s="1">
@@ -1335,18 +1443,21 @@
       <c r="F18" s="1">
         <v>0</v>
       </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="14">
         <v>45762</v>
       </c>
       <c r="D19" s="1">
@@ -1358,18 +1469,21 @@
       <c r="F19" s="1">
         <v>0</v>
       </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="14">
         <v>45763</v>
       </c>
       <c r="D20" s="1">
@@ -1381,18 +1495,21 @@
       <c r="F20" s="1">
         <v>0</v>
       </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="14">
         <v>45764</v>
       </c>
       <c r="D21" s="1">
@@ -1404,18 +1521,21 @@
       <c r="F21" s="1">
         <v>0</v>
       </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="14">
         <v>45765</v>
       </c>
       <c r="D22" s="1">
@@ -1427,18 +1547,21 @@
       <c r="F22" s="1">
         <v>0</v>
       </c>
-      <c r="G22" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="14">
         <v>45768</v>
       </c>
       <c r="D23" s="1">
@@ -1450,18 +1573,21 @@
       <c r="F23" s="1">
         <v>0</v>
       </c>
-      <c r="G23" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>1</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="14">
         <v>45769</v>
       </c>
       <c r="D24" s="1">
@@ -1473,11 +1599,14 @@
       <c r="F24" s="1">
         <v>0</v>
       </c>
-      <c r="G24" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>1</v>
       </c>
@@ -1496,18 +1625,21 @@
       <c r="F25" s="1">
         <v>0</v>
       </c>
-      <c r="G25" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1">
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>1</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="14">
         <v>45771</v>
       </c>
       <c r="D26" s="1">
@@ -1519,41 +1651,47 @@
       <c r="F26" s="1">
         <v>0</v>
       </c>
-      <c r="G26" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="17">
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="15">
         <v>2</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="16">
         <v>45898</v>
       </c>
       <c r="D27" s="11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F27" s="11">
         <v>0</v>
       </c>
-      <c r="G27" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="G27" s="11">
+        <v>0</v>
+      </c>
+      <c r="H27" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>2</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="14">
         <v>45901</v>
       </c>
       <c r="D28" s="1">
@@ -1565,18 +1703,21 @@
       <c r="F28" s="1">
         <v>70</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>2</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="14">
         <v>45902</v>
       </c>
       <c r="D29" s="1">
@@ -1588,18 +1729,21 @@
       <c r="F29" s="1">
         <v>70</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>2</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="14">
         <v>45903</v>
       </c>
       <c r="D30" s="1">
@@ -1611,18 +1755,21 @@
       <c r="F30" s="1">
         <v>70</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>2</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="14">
         <v>45904</v>
       </c>
       <c r="D31" s="1">
@@ -1634,18 +1781,21 @@
       <c r="F31" s="1">
         <v>70</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>2</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="14">
         <v>45905</v>
       </c>
       <c r="D32" s="1">
@@ -1657,19 +1807,22 @@
       <c r="F32" s="1">
         <v>70</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>2</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="16">
-        <v>45909</v>
+      <c r="C33" s="14">
+        <v>45908</v>
       </c>
       <c r="D33" s="1">
         <v>6</v>
@@ -1680,19 +1833,22 @@
       <c r="F33" s="1">
         <v>70</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>2</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="16">
-        <v>45910</v>
+      <c r="C34" s="14">
+        <v>45909</v>
       </c>
       <c r="D34" s="1">
         <v>7</v>
@@ -1703,19 +1859,22 @@
       <c r="F34" s="1">
         <v>70</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>2</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="16">
-        <v>45911</v>
+      <c r="C35" s="14">
+        <v>45910</v>
       </c>
       <c r="D35" s="1">
         <v>8</v>
@@ -1726,19 +1885,22 @@
       <c r="F35" s="1">
         <v>70</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>2</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="16">
-        <v>45912</v>
+      <c r="C36" s="14">
+        <v>45911</v>
       </c>
       <c r="D36" s="1">
         <v>9</v>
@@ -1749,19 +1911,22 @@
       <c r="F36" s="1">
         <v>70</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>2</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="16">
-        <v>45913</v>
+      <c r="C37" s="14">
+        <v>45912</v>
       </c>
       <c r="D37" s="1">
         <v>10</v>
@@ -1772,18 +1937,21 @@
       <c r="F37" s="1">
         <v>70</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>2</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="14">
         <v>45915</v>
       </c>
       <c r="D38" s="1">
@@ -1795,18 +1963,21 @@
       <c r="F38" s="1">
         <v>70</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>2</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="14">
         <v>45916</v>
       </c>
       <c r="D39" s="1">
@@ -1818,18 +1989,21 @@
       <c r="F39" s="1">
         <v>70</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>2</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="14">
         <v>45917</v>
       </c>
       <c r="D40" s="1">
@@ -1841,18 +2015,21 @@
       <c r="F40" s="1">
         <v>70</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>2</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="14">
         <v>45918</v>
       </c>
       <c r="D41" s="1">
@@ -1864,18 +2041,21 @@
       <c r="F41" s="1">
         <v>70</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>2</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="14">
         <v>45919</v>
       </c>
       <c r="D42" s="1">
@@ -1887,18 +2067,21 @@
       <c r="F42" s="1">
         <v>70</v>
       </c>
-      <c r="G42" s="13">
+      <c r="G42" s="1">
         <v>4.8939999999999997E-2</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>2</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="14">
         <v>45922</v>
       </c>
       <c r="D43" s="1">
@@ -1910,18 +2093,21 @@
       <c r="F43" s="1">
         <v>0</v>
       </c>
-      <c r="G43" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>2</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="14">
         <v>45923</v>
       </c>
       <c r="D44" s="1">
@@ -1933,18 +2119,21 @@
       <c r="F44" s="1">
         <v>0</v>
       </c>
-      <c r="G44" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>2</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="14">
         <v>45924</v>
       </c>
       <c r="D45" s="1">
@@ -1956,18 +2145,21 @@
       <c r="F45" s="1">
         <v>0</v>
       </c>
-      <c r="G45" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>2</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="14">
         <v>45925</v>
       </c>
       <c r="D46" s="1">
@@ -1979,18 +2171,21 @@
       <c r="F46" s="1">
         <v>0</v>
       </c>
-      <c r="G46" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>2</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="14">
         <v>45926</v>
       </c>
       <c r="D47" s="1">
@@ -2002,18 +2197,21 @@
       <c r="F47" s="1">
         <v>0</v>
       </c>
-      <c r="G47" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>2</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="14">
         <v>45929</v>
       </c>
       <c r="D48" s="1">
@@ -2025,18 +2223,21 @@
       <c r="F48" s="1">
         <v>0</v>
       </c>
-      <c r="G48" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>2</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="14">
         <v>45930</v>
       </c>
       <c r="D49" s="1">
@@ -2048,18 +2249,21 @@
       <c r="F49" s="1">
         <v>0</v>
       </c>
-      <c r="G49" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>2</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="14">
         <v>45931</v>
       </c>
       <c r="D50" s="1">
@@ -2071,588 +2275,704 @@
       <c r="F50" s="1">
         <v>0</v>
       </c>
-      <c r="G50" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1">
-      <c r="A51" s="14">
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
         <v>2</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="20">
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="14">
         <v>45932</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="1">
         <v>24</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="4">
-        <v>0</v>
-      </c>
-      <c r="G51" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="1">
-        <v>7</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
+        <v>7</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="11">
+        <v>1</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="11">
+        <v>70</v>
+      </c>
+      <c r="G52" s="11">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H52" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="10">
+        <v>7</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="1">
-        <v>1</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="D53" s="23">
+        <v>2</v>
+      </c>
+      <c r="E53" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="1">
-        <v>70</v>
-      </c>
-      <c r="G52" s="1">
+      <c r="F53" s="23">
+        <v>70</v>
+      </c>
+      <c r="G53" s="23">
         <v>5.1609700000000001E-2</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="15">
-      <c r="A53" s="1">
-        <v>7</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="H53" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="10">
+        <v>7</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="1">
-        <v>2</v>
-      </c>
-      <c r="E53" s="21" t="s">
+      <c r="D54" s="23">
+        <v>3</v>
+      </c>
+      <c r="E54" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="1">
-        <v>70</v>
-      </c>
-      <c r="G53" s="1">
+      <c r="F54" s="23">
+        <v>70</v>
+      </c>
+      <c r="G54" s="23">
         <v>5.1609700000000001E-2</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="15">
-      <c r="A54" s="1">
-        <v>7</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="H54" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="10">
+        <v>7</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D54" s="1">
-        <v>3</v>
-      </c>
-      <c r="E54" s="21" t="s">
+      <c r="D55" s="23">
+        <v>4</v>
+      </c>
+      <c r="E55" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="1">
-        <v>70</v>
-      </c>
-      <c r="G54" s="1">
+      <c r="F55" s="23">
+        <v>70</v>
+      </c>
+      <c r="G55" s="23">
         <v>5.1609700000000001E-2</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="15">
-      <c r="A55" s="1">
-        <v>7</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="H55" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="10">
+        <v>7</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D55" s="1">
-        <v>4</v>
-      </c>
-      <c r="E55" s="21" t="s">
+      <c r="D56" s="23">
+        <v>5</v>
+      </c>
+      <c r="E56" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="1">
-        <v>70</v>
-      </c>
-      <c r="G55" s="1">
+      <c r="F56" s="23">
+        <v>70</v>
+      </c>
+      <c r="G56" s="23">
         <v>5.1609700000000001E-2</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="15">
-      <c r="A56" s="1">
-        <v>7</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="H56" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="10">
+        <v>7</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="1">
-        <v>5</v>
-      </c>
-      <c r="E56" s="21" t="s">
+      <c r="D57" s="23">
+        <v>6</v>
+      </c>
+      <c r="E57" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="23">
+        <v>70</v>
+      </c>
+      <c r="G57" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H57" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="10">
+        <v>7</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="23">
+        <v>7</v>
+      </c>
+      <c r="E58" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="23">
+        <v>70</v>
+      </c>
+      <c r="G58" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H58" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="10">
+        <v>7</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="23">
         <v>8</v>
       </c>
-      <c r="F56" s="1">
-        <v>70</v>
-      </c>
-      <c r="G56" s="1">
+      <c r="E59" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="23">
+        <v>70</v>
+      </c>
+      <c r="G59" s="23">
         <v>5.1609700000000001E-2</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="15">
-      <c r="A57" s="1">
-        <v>7</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="H59" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="10">
+        <v>7</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="23">
+        <v>9</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="23">
+        <v>70</v>
+      </c>
+      <c r="G60" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H60" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="10">
+        <v>7</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" s="23">
+        <v>10</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="23">
+        <v>70</v>
+      </c>
+      <c r="G61" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H61" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="10">
+        <v>7</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" s="23">
+        <v>11</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="23">
+        <v>70</v>
+      </c>
+      <c r="G62" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H62" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
+        <v>7</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" s="23">
+        <v>12</v>
+      </c>
+      <c r="E63" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="23">
+        <v>70</v>
+      </c>
+      <c r="G63" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H63" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
+        <v>7</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" s="23">
+        <v>13</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="23">
+        <v>70</v>
+      </c>
+      <c r="G64" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H64" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>7</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" s="23">
+        <v>14</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="23">
+        <v>70</v>
+      </c>
+      <c r="G65" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H65" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="10">
+        <v>7</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D66" s="23">
+        <v>15</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="23">
+        <v>70</v>
+      </c>
+      <c r="G66" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H66" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="10">
+        <v>7</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" s="23">
+        <v>16</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="23">
+        <v>0</v>
+      </c>
+      <c r="G67" s="23">
+        <v>5.1609700000000001E-2</v>
+      </c>
+      <c r="H67" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
+        <v>7</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="23">
+        <v>17</v>
+      </c>
+      <c r="E68" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="23">
+        <v>0</v>
+      </c>
+      <c r="G68" s="23">
+        <v>0</v>
+      </c>
+      <c r="H68" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
+        <v>7</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69" s="23">
+        <v>18</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="23">
+        <v>0</v>
+      </c>
+      <c r="G69" s="23">
+        <v>0</v>
+      </c>
+      <c r="H69" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
+        <v>7</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D70" s="23">
         <v>19</v>
       </c>
-      <c r="D57" s="1">
-        <v>6</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="1">
-        <v>70</v>
-      </c>
-      <c r="G57" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15">
-      <c r="A58" s="1">
-        <v>7</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="E70" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="23">
+        <v>0</v>
+      </c>
+      <c r="G70" s="23">
+        <v>0</v>
+      </c>
+      <c r="H70" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="10">
+        <v>7</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" s="23">
         <v>20</v>
       </c>
-      <c r="D58" s="1">
-        <v>7</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="1">
-        <v>70</v>
-      </c>
-      <c r="G58" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15">
-      <c r="A59" s="1">
-        <v>7</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="E71" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="23">
+        <v>0</v>
+      </c>
+      <c r="G71" s="23">
+        <v>0</v>
+      </c>
+      <c r="H71" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="10">
+        <v>7</v>
+      </c>
+      <c r="B72" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" s="23">
         <v>21</v>
       </c>
-      <c r="D59" s="1">
-        <v>8</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="1">
-        <v>70</v>
-      </c>
-      <c r="G59" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15">
-      <c r="A60" s="1">
-        <v>7</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="E72" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="23">
+        <v>0</v>
+      </c>
+      <c r="G72" s="23">
+        <v>0</v>
+      </c>
+      <c r="H72" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="10">
+        <v>7</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="23">
         <v>22</v>
       </c>
-      <c r="D60" s="1">
-        <v>9</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="1">
-        <v>70</v>
-      </c>
-      <c r="G60" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15">
-      <c r="A61" s="1">
-        <v>7</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="E73" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="23">
+        <v>0</v>
+      </c>
+      <c r="G73" s="23">
+        <v>0</v>
+      </c>
+      <c r="H73" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="13">
+        <v>7</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D74" s="4">
         <v>23</v>
       </c>
-      <c r="D61" s="1">
+      <c r="E74" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="1">
-        <v>70</v>
-      </c>
-      <c r="G61" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15">
-      <c r="A62" s="1">
-        <v>7</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4">
+        <v>0</v>
+      </c>
+      <c r="H74" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="13">
+        <v>7</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D75" s="4">
         <v>24</v>
       </c>
-      <c r="D62" s="1">
-        <v>11</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="1">
-        <v>70</v>
-      </c>
-      <c r="G62" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15">
-      <c r="A63" s="1">
-        <v>7</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D63" s="1">
+      <c r="E75" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E63" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" s="1">
-        <v>70</v>
-      </c>
-      <c r="G63" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15">
-      <c r="A64" s="1">
-        <v>7</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D64" s="1">
-        <v>13</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="1">
-        <v>70</v>
-      </c>
-      <c r="G64" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15">
-      <c r="A65" s="1">
-        <v>7</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D65" s="1">
-        <v>14</v>
-      </c>
-      <c r="E65" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="1">
-        <v>70</v>
-      </c>
-      <c r="G65" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15">
-      <c r="A66" s="1">
-        <v>7</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D66" s="1">
-        <v>15</v>
-      </c>
-      <c r="E66" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="1">
-        <v>70</v>
-      </c>
-      <c r="G66" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="1">
-        <v>7</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D67" s="1">
-        <v>16</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>5.1609700000000001E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15">
-      <c r="A68" s="1">
-        <v>7</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D68" s="1">
-        <v>17</v>
-      </c>
-      <c r="E68" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15">
-      <c r="A69" s="1">
-        <v>7</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D69" s="1">
-        <v>18</v>
-      </c>
-      <c r="E69" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" s="1">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15">
-      <c r="A70" s="1">
-        <v>7</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D70" s="1">
-        <v>19</v>
-      </c>
-      <c r="E70" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15">
-      <c r="A71" s="1">
-        <v>7</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D71" s="1">
-        <v>20</v>
-      </c>
-      <c r="E71" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="1">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15">
-      <c r="A72" s="1">
-        <v>7</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D72" s="1">
-        <v>21</v>
-      </c>
-      <c r="E72" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="1">
-        <v>7</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D73" s="1">
-        <v>22</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="1">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="C74" s="2"/>
-      <c r="E74" s="5"/>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="C75" s="2"/>
-      <c r="E75" s="5"/>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4">
+        <v>0</v>
+      </c>
+      <c r="H75" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C76" s="2"/>
       <c r="E76" s="5"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C77" s="2"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C78" s="2"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C79" s="2"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C80" s="2"/>
       <c r="E80" s="5"/>
     </row>
-    <row r="81" spans="3:6">
+    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C81" s="2"/>
       <c r="E81" s="5"/>
     </row>
-    <row r="82" spans="3:6">
+    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C82" s="2"/>
       <c r="E82" s="5"/>
     </row>
-    <row r="83" spans="3:6">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C83" s="2"/>
       <c r="E83" s="5"/>
     </row>
-    <row r="84" spans="3:6">
+    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C84" s="2"/>
       <c r="E84" s="5"/>
     </row>
-    <row r="85" spans="3:6">
+    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C85" s="2"/>
       <c r="E85" s="5"/>
     </row>
-    <row r="86" spans="3:6" ht="15" thickBot="1">
+    <row r="86" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C86" s="2"/>
       <c r="F86" s="4"/>
     </row>
